--- a/docs/dataset/RADAR_Test_QMRA.xlsx
+++ b/docs/dataset/RADAR_Test_QMRA.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -48,9 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I204"/>
+  <dimension ref="A1:I224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -425,14 +427,6 @@
           <t>QMRA Input Template v1.0</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -440,26 +434,8 @@
           <t>For use with the AMR-TOOL QMRA module</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -8705,6 +8681,826 @@
       </c>
       <c r="I204" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="n">
+        <v>45296</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>530.836</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="n">
+        <v>45314</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>517.9930000000001</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="n">
+        <v>45332</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>545.832</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>45350</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>1089.654</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="n">
+        <v>45368</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>538.3339999999999</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>45386</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>168.036</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>795.842</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="n">
+        <v>45422</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>478.039</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="n">
+        <v>45440</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>498.954</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="n">
+        <v>45458</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>662.11</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="n">
+        <v>45476</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>730.978</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="n">
+        <v>45494</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>1613.167</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="n">
+        <v>45512</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>1048.453</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="n">
+        <v>45530</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>659.09</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="n">
+        <v>45548</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>320.331</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>253.273</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="n">
+        <v>45584</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>739.756</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="n">
+        <v>45602</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>1828.678</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="n">
+        <v>45620</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>621.626</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="n">
+        <v>45638</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Secondary Contact (Kayaking/Wading)</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Infection</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>548.153</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>CFU/100ml</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
